--- a/_data_list/FF_PT.xlsx
+++ b/_data_list/FF_PT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D8AA8-BC15-4D96-9A85-0513C8CC72AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F5440D-BAA6-47AC-B3A0-F956E3A70366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="169">
   <si>
     <t>DMS_CODE</t>
   </si>
@@ -1494,7 +1494,12 @@
       <c r="O9" s="8">
         <v>7824872522</v>
       </c>
-      <c r="Q9" s="9"/>
+      <c r="P9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>2311030553506</v>
+      </c>
       <c r="T9" s="6" t="s">
         <v>158</v>
       </c>
